--- a/exports/exhibit-by-cpl-type.xlsx
+++ b/exports/exhibit-by-cpl-type.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credit Recommendations by CPL T" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Recommendations by CPL T" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/exhibit-by-cpl-type.xlsx
+++ b/exports/exhibit-by-cpl-type.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Recommendations by CPL T" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Credit Recommendations by CPL T" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5654</v>
+        <v>5755</v>
       </c>
       <c r="C2" t="n">
-        <v>1099</v>
+        <v>1117</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="3">
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3101</v>
+        <v>3152</v>
       </c>
       <c r="C3" t="n">
-        <v>899</v>
+        <v>923</v>
       </c>
       <c r="D3" t="n">
         <v>77</v>
       </c>
       <c r="E3" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1490</v>
+        <v>1524</v>
       </c>
       <c r="C4" t="n">
-        <v>1080</v>
+        <v>1114</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C5" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
         <v>3.4</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10760</v>
+        <v>11004</v>
       </c>
       <c r="C8" t="n">
-        <v>3451</v>
+        <v>3535</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
